--- a/per-stock/NBIS/financials.xlsx
+++ b/per-stock/NBIS/financials.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (annual)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (quarterly)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet (annual)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (annual)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data flags" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FY Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Income stmt (annual)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Income stmt (quarterly)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Balance sheet (annual)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Balance sheet (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cash flow (annual)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cash flow (quarterly)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Data flags" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -61,11 +67,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,7 +540,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>55842369536</v>
+        <v>72790073344</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -546,7 +555,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>56513536000</v>
+        <v>73640935424</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -561,7 +570,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>84.59231</v>
+        <v>111.12016</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -576,7 +585,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>608.88104</v>
+        <v>793.67145</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -591,7 +600,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>63.60903</v>
+        <v>82.91385</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -666,7 +675,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6.215</v>
+        <v>6.839</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -681,7 +690,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>9298199552</v>
+        <v>9373200384</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -696,7 +705,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>9496200192</v>
+        <v>9590400000</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -711,11 +720,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-6128775168</v>
+        <v>-3154700000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>yfinance info.freeCashflow</t>
+          <t>statement: TTM OCF - |capex| (yfinance quarterly_cashflow)</t>
         </is>
       </c>
     </row>
@@ -741,7 +750,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>219.94</v>
+        <v>286.69</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -785,6 +794,477 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fiscal-year summary (GAAP, $ except where noted)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FY-3</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FY-2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FY-1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TTM</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source / formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fiscal period end</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TTM → 2026-03-31</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>annual statement headers; TTM = Σ last 4 quarters</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>'Income stmt (annual)'!D56</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>'Income stmt (annual)'!C56</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>'Income stmt (annual)'!B56</f>
+        <v/>
+      </c>
+      <c r="E3" s="3">
+        <f>SUM('Income stmt (quarterly)'!B46:E46)</f>
+        <v/>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>'Income stmt (annual)'!D54</f>
+        <v/>
+      </c>
+      <c r="C4" s="3">
+        <f>'Income stmt (annual)'!C54</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>'Income stmt (annual)'!B54</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>SUM('Income stmt (quarterly)'!B44:E44)</f>
+        <v/>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gross Profit (GAAP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>IFERROR(B4/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="4">
+        <f>IFERROR(C4/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>IFERROR(D4/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>IFERROR(E4/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>GAAP = gross profit / revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>'Income stmt (annual)'!D45</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>'Income stmt (annual)'!C45</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>'Income stmt (annual)'!B45</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>SUM('Income stmt (quarterly)'!B38:E38)</f>
+        <v/>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <f>IFERROR(B6/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="4">
+        <f>IFERROR(C6/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="4">
+        <f>IFERROR(D6/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="4">
+        <f>IFERROR(E6/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f> operating income / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>'Income stmt (annual)'!D10</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>'Income stmt (annual)'!C10</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>'Income stmt (annual)'!B10</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>SUM('Income stmt (quarterly)'!B10:E10)</f>
+        <v/>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Free cash flow</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>'Cash flow (annual)'!D2</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>'Cash flow (annual)'!C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>'Cash flow (annual)'!B2</f>
+        <v/>
+      </c>
+      <c r="E9" s="3">
+        <f>SUM('Cash flow (quarterly)'!B2:E2)</f>
+        <v/>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FCF = OCF − capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FCF margin %</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>IFERROR(B9/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="4">
+        <f>IFERROR(C9/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="4">
+        <f>IFERROR(D9/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>IFERROR(E9/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f> FCF / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>-'Cash flow (annual)'!D7</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>-'Cash flow (annual)'!C7</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>-'Cash flow (annual)'!B7</f>
+        <v/>
+      </c>
+      <c r="E11" s="3">
+        <f>-SUM('Cash flow (quarterly)'!B6:E6)</f>
+        <v/>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Capex (shown positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Capex / revenue %</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <f>IFERROR(B11/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="4">
+        <f>IFERROR(C11/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="4">
+        <f>IFERROR(D11/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="4">
+        <f>IFERROR(E11/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f> capex / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>'Balance sheet (annual)'!D5</f>
+        <v/>
+      </c>
+      <c r="C13" s="3">
+        <f>'Balance sheet (annual)'!C5</f>
+        <v/>
+      </c>
+      <c r="D13" s="3">
+        <f>'Balance sheet (annual)'!B5</f>
+        <v/>
+      </c>
+      <c r="E13" s="3">
+        <f>'Balance sheet (quarterly)'!B5</f>
+        <v/>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Net debt; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" s="5">
+        <f>IFERROR(B13/B8,"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="5">
+        <f>IFERROR(C13/C8,"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>IFERROR(D13/D8,"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>IFERROR(E13/E8,"")</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f> net debt / EBITDA</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Share count (period-end, M)</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>'Balance sheet (annual)'!D3/1e6</f>
+        <v/>
+      </c>
+      <c r="C15" s="6">
+        <f>'Balance sheet (annual)'!C3/1e6</f>
+        <v/>
+      </c>
+      <c r="D15" s="6">
+        <f>'Balance sheet (annual)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="E15" s="6">
+        <f>'Balance sheet (quarterly)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>shares ÷ 1e6; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Share count YoY %</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4">
+        <f>IFERROR(C15/B15-1,"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="4">
+        <f>IFERROR(D15/C15-1,"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="4">
+        <f>IFERROR(E15/D15-1,"")</f>
+        <v/>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vs prior period</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1180,13 +1660,13 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>247679946</v>
+        <v>253016971</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>281005226</v>
+        <v>235753600</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>370839686</v>
+        <v>373059228</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>377020285</v>
@@ -1200,10 +1680,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>242531291</v>
+        <v>253016971</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>281005226</v>
+        <v>235753600</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>370839686</v>
@@ -1220,13 +1700,13 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0.33</v>
+        <v>0.401949</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>-2.28</v>
+        <v>-2.735059</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>0.65</v>
+        <v>0.6017400000000001</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>1.107785</v>
@@ -1240,13 +1720,13 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>0.34</v>
+        <v>0.401949</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>-2.28</v>
+        <v>-2.735059</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>0.65</v>
+        <v>0.605355</v>
       </c>
       <c r="E22" s="3" t="n">
         <v>1.439463</v>
@@ -1934,7 +2414,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1960,27 +2440,27 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-06-30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-03-31</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>2024-12-31</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -1996,13 +2476,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>312240000</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>6450000</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>65554.628857</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>0</v>
@@ -2019,19 +2499,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>0.258</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>0.002502</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>0.001561</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="F3" s="3" t="n">
         <v>0.258</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>0.012518</v>
       </c>
       <c r="G3" s="3" t="n"/>
     </row>
@@ -2042,19 +2522,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>140300000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>-33300000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>-19600000</v>
       </c>
-      <c r="D4" s="3" t="n">
-        <v>609300000</v>
-      </c>
       <c r="E4" s="3" t="n">
-        <v>-80300000</v>
+        <v>618900000</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>-112000000</v>
+        <v>-47300000</v>
       </c>
       <c r="G4" s="3" t="n"/>
     </row>
@@ -2065,15 +2545,17 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>780600000</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>25000000</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>26200000</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>597400000</v>
       </c>
-      <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="n"/>
       <c r="G5" s="3" t="n">
         <v>5600000</v>
@@ -2086,15 +2568,17 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>780600000</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>25000000</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>26200000</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>597400000</v>
       </c>
-      <c r="E6" s="3" t="n"/>
       <c r="F6" s="3" t="n"/>
       <c r="G6" s="3" t="n">
         <v>5600000</v>
@@ -2107,19 +2591,19 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>621200000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>-268800000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>-119600000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>511800000</v>
       </c>
-      <c r="E7" s="3" t="n">
-        <v>-113600000</v>
-      </c>
       <c r="F7" s="3" t="n">
-        <v>-134100000</v>
+        <v>-104300000</v>
       </c>
       <c r="G7" s="3" t="n"/>
     </row>
@@ -2130,19 +2614,19 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>241800000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>215900000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>111800000</v>
       </c>
-      <c r="D8" s="3" t="n">
-        <v>75100000</v>
-      </c>
       <c r="E8" s="3" t="n">
-        <v>49200000</v>
+        <v>84700000</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>37300000</v>
+        <v>56100000</v>
       </c>
       <c r="G8" s="3" t="n"/>
     </row>
@@ -2153,19 +2637,19 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>74000000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>47200000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>30100000</v>
       </c>
-      <c r="D9" s="3" t="n">
-        <v>25300000</v>
-      </c>
       <c r="E9" s="3" t="n">
-        <v>29500000</v>
+        <v>15700000</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>23600000</v>
+        <v>17700000</v>
       </c>
       <c r="G9" s="3" t="n"/>
     </row>
@@ -2176,19 +2660,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>920900000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>-8300000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>6600000</v>
       </c>
-      <c r="D10" s="3" t="n">
-        <v>609300000</v>
-      </c>
       <c r="E10" s="3" t="n">
-        <v>-80300000</v>
+        <v>618900000</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>-112000000</v>
+        <v>-47300000</v>
       </c>
       <c r="G10" s="3" t="n"/>
     </row>
@@ -2199,19 +2683,19 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>679100000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>-224200000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>-105200000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>534200000</v>
       </c>
-      <c r="E11" s="3" t="n">
-        <v>-129500000</v>
-      </c>
       <c r="F11" s="3" t="n">
-        <v>-149300000</v>
+        <v>-103400000</v>
       </c>
       <c r="G11" s="3" t="n"/>
     </row>
@@ -2222,19 +2706,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>-49500000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>-28500000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>-8500000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>-1300000</v>
       </c>
-      <c r="E12" s="3" t="n">
-        <v>8600000</v>
-      </c>
       <c r="F12" s="3" t="n">
-        <v>21900000</v>
+        <v>8500000</v>
       </c>
       <c r="G12" s="3" t="n"/>
     </row>
@@ -2245,19 +2729,21 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>63700000</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>42000000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>14700000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>4800000</v>
       </c>
-      <c r="E13" s="3" t="n"/>
-      <c r="F13" s="3" t="n"/>
-      <c r="G13" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="F13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2266,19 +2752,19 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>14200000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>13500000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>6200000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>3500000</v>
       </c>
-      <c r="E14" s="3" t="n">
-        <v>8600000</v>
-      </c>
       <c r="F14" s="3" t="n">
-        <v>21900000</v>
+        <v>8500000</v>
       </c>
       <c r="G14" s="3" t="n"/>
     </row>
@@ -2289,19 +2775,19 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>152840000</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>-287350000</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>-145734445.371143</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>511800000</v>
       </c>
-      <c r="E15" s="3" t="n">
-        <v>-113600000</v>
-      </c>
       <c r="F15" s="3" t="n">
-        <v>-134100000</v>
+        <v>-104300000</v>
       </c>
       <c r="G15" s="3" t="n"/>
     </row>
@@ -2312,19 +2798,19 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>621200000</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>-268800000</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>-119600000</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="E16" s="3" t="n">
         <v>584500000</v>
       </c>
-      <c r="E16" s="3" t="n">
-        <v>-113600000</v>
-      </c>
       <c r="F16" s="3" t="n">
-        <v>-133200000</v>
+        <v>-113500000</v>
       </c>
       <c r="G16" s="3" t="n"/>
     </row>
@@ -2335,19 +2821,19 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>527000000</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>477700000</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="D17" s="3" t="n">
         <v>276300000</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>202700000</v>
       </c>
-      <c r="E17" s="3" t="n">
-        <v>184800000</v>
-      </c>
       <c r="F17" s="3" t="n">
-        <v>187200000</v>
+        <v>171200000</v>
       </c>
       <c r="G17" s="3" t="n"/>
     </row>
@@ -2358,19 +2844,19 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
+        <v>-128000000</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>-250000000</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>-130200000</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>-102000000</v>
       </c>
-      <c r="E18" s="3" t="n">
-        <v>-129500000</v>
-      </c>
       <c r="F18" s="3" t="n">
-        <v>-149300000</v>
+        <v>-120300000</v>
       </c>
       <c r="G18" s="3" t="n"/>
     </row>
@@ -2381,19 +2867,19 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
+        <v>308971701</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>253016971</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="D19" s="3" t="n">
         <v>241071190</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>238705092</v>
       </c>
-      <c r="E19" s="3" t="n">
-        <v>238108831</v>
-      </c>
       <c r="F19" s="3" t="n">
-        <v>235753600</v>
+        <v>237916047</v>
       </c>
       <c r="G19" s="3" t="n"/>
     </row>
@@ -2404,19 +2890,19 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
+        <v>258298911</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>253016971</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>205831526</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>238705092</v>
       </c>
-      <c r="E20" s="3" t="n">
-        <v>238108831</v>
-      </c>
       <c r="F20" s="3" t="n">
-        <v>235753600</v>
+        <v>237916047</v>
       </c>
       <c r="G20" s="3" t="n"/>
     </row>
@@ -2427,19 +2913,19 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>-0.986495</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="D21" s="3" t="n">
         <v>-0.5</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>2.437401</v>
       </c>
-      <c r="E21" s="3" t="n">
-        <v>-0.477093</v>
-      </c>
       <c r="F21" s="3" t="n">
-        <v>-0.579419</v>
+        <v>-0.48</v>
       </c>
       <c r="G21" s="3" t="n"/>
     </row>
@@ -2450,19 +2936,19 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>-0.986495</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>-0.5</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>2.448209</v>
       </c>
-      <c r="E22" s="3" t="n">
-        <v>-0.477093</v>
-      </c>
       <c r="F22" s="3" t="n">
-        <v>-0.579419</v>
+        <v>-0.48</v>
       </c>
       <c r="G22" s="3" t="n"/>
     </row>
@@ -2473,19 +2959,19 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>621200000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>-268800000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>-119600000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>584500000</v>
       </c>
-      <c r="E23" s="3" t="n">
-        <v>-113600000</v>
-      </c>
       <c r="F23" s="3" t="n">
-        <v>-133200000</v>
+        <v>-113500000</v>
       </c>
       <c r="G23" s="3" t="n"/>
     </row>
@@ -2496,19 +2982,19 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>621200000</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>-268800000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>-119600000</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>584500000</v>
       </c>
-      <c r="E24" s="3" t="n">
-        <v>-113600000</v>
-      </c>
       <c r="F24" s="3" t="n">
-        <v>-133200000</v>
+        <v>-113500000</v>
       </c>
       <c r="G24" s="3" t="n"/>
     </row>
@@ -2519,19 +3005,19 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
+        <v>621200000</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>-268800000</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>-119600000</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>584500000</v>
       </c>
-      <c r="E25" s="3" t="n">
-        <v>-113600000</v>
-      </c>
       <c r="F25" s="3" t="n">
-        <v>-133200000</v>
+        <v>-113500000</v>
       </c>
       <c r="G25" s="3" t="n"/>
     </row>
@@ -2542,19 +3028,19 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
+        <v>621200000</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>-268800000</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>-119600000</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>584500000</v>
       </c>
-      <c r="E26" s="3" t="n">
-        <v>-113600000</v>
-      </c>
       <c r="F26" s="3" t="n">
-        <v>-133200000</v>
+        <v>-113500000</v>
       </c>
       <c r="G26" s="3" t="n"/>
     </row>
@@ -2571,13 +3057,13 @@
         <v>0</v>
       </c>
       <c r="D27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3" t="n">
         <v>72700000</v>
       </c>
-      <c r="E27" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="F27" s="3" t="n">
-        <v>900000</v>
+        <v>-9200000</v>
       </c>
       <c r="G27" s="3" t="n"/>
     </row>
@@ -2588,19 +3074,19 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
+        <v>621200000</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>-268800000</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="D28" s="3" t="n">
         <v>-119600000</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="E28" s="3" t="n">
         <v>511800000</v>
       </c>
-      <c r="E28" s="3" t="n">
-        <v>-113600000</v>
-      </c>
       <c r="F28" s="3" t="n">
-        <v>-134100000</v>
+        <v>-104300000</v>
       </c>
       <c r="G28" s="3" t="n"/>
     </row>
@@ -2611,19 +3097,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>-5800000</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>2600000</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>-300000</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>800000</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>900000</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>-1700000</v>
       </c>
       <c r="G29" s="3" t="n"/>
     </row>
@@ -2634,19 +3120,19 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
+        <v>615400000</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>-266200000</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="D30" s="3" t="n">
         <v>-119900000</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>512600000</v>
       </c>
-      <c r="E30" s="3" t="n">
-        <v>-112700000</v>
-      </c>
       <c r="F30" s="3" t="n">
-        <v>-135800000</v>
+        <v>-103400000</v>
       </c>
       <c r="G30" s="3" t="n"/>
     </row>
@@ -2657,19 +3143,19 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
+        <v>792900000</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>12300000</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="D31" s="3" t="n">
         <v>18800000</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>615900000</v>
       </c>
-      <c r="E31" s="3" t="n">
-        <v>8200000</v>
-      </c>
       <c r="F31" s="3" t="n">
-        <v>-8400000</v>
+        <v>8400000</v>
       </c>
       <c r="G31" s="3" t="n"/>
     </row>
@@ -2680,19 +3166,19 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
+        <v>19900000</v>
+      </c>
+      <c r="C32" s="3" t="n">
         <v>-2100000</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="D32" s="3" t="n">
         <v>100000</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="E32" s="3" t="n">
         <v>-7900000</v>
       </c>
-      <c r="E32" s="3" t="n">
-        <v>8100000</v>
-      </c>
       <c r="F32" s="3" t="n">
-        <v>9100000</v>
+        <v>8300000</v>
       </c>
       <c r="G32" s="3" t="n"/>
     </row>
@@ -2703,19 +3189,19 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
+        <v>-7600000</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>-10600000</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="D33" s="3" t="n">
         <v>-7500000</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>-6300000</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="F33" s="3" t="n">
         <v>100000</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="G33" s="3" t="n"/>
     </row>
@@ -2726,15 +3212,17 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>780600000</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>25000000</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="D34" s="3" t="n">
         <v>26200000</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="E34" s="3" t="n">
         <v>597400000</v>
       </c>
-      <c r="E34" s="3" t="n"/>
       <c r="F34" s="3" t="n"/>
       <c r="G34" s="3" t="n">
         <v>5600000</v>
@@ -2747,19 +3235,19 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
+        <v>-49500000</v>
+      </c>
+      <c r="C35" s="3" t="n">
         <v>-28500000</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="D35" s="3" t="n">
         <v>-8500000</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="E35" s="3" t="n">
         <v>-1300000</v>
       </c>
-      <c r="E35" s="3" t="n">
-        <v>8600000</v>
-      </c>
       <c r="F35" s="3" t="n">
-        <v>21900000</v>
+        <v>8500000</v>
       </c>
       <c r="G35" s="3" t="n"/>
     </row>
@@ -2770,19 +3258,21 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>63700000</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>42000000</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>14700000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>4800000</v>
       </c>
-      <c r="E36" s="3" t="n"/>
-      <c r="F36" s="3" t="n"/>
-      <c r="G36" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="F36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2791,19 +3281,19 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>14200000</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>13500000</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>6200000</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>3500000</v>
       </c>
-      <c r="E37" s="3" t="n">
-        <v>8600000</v>
-      </c>
       <c r="F37" s="3" t="n">
-        <v>21900000</v>
+        <v>8500000</v>
       </c>
       <c r="G37" s="3" t="n"/>
     </row>
@@ -2814,19 +3304,19 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
+        <v>-128000000</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>-250000000</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>-130200000</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>-102000000</v>
       </c>
-      <c r="E38" s="3" t="n">
-        <v>-129500000</v>
-      </c>
       <c r="F38" s="3" t="n">
-        <v>-149300000</v>
+        <v>-120300000</v>
       </c>
       <c r="G38" s="3" t="n"/>
     </row>
@@ -2837,19 +3327,19 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
+        <v>423200000</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>409200000</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>233400000</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="E39" s="3" t="n">
         <v>177400000</v>
       </c>
-      <c r="E39" s="3" t="n">
-        <v>155300000</v>
-      </c>
       <c r="F39" s="3" t="n">
-        <v>159700000</v>
+        <v>146500000</v>
       </c>
       <c r="G39" s="3" t="n"/>
     </row>
@@ -2860,19 +3350,19 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
+        <v>212000000</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>194600000</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>99000000</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>75100000</v>
       </c>
-      <c r="E40" s="3" t="n">
-        <v>49200000</v>
-      </c>
       <c r="F40" s="3" t="n">
-        <v>33400000</v>
+        <v>49100000</v>
       </c>
       <c r="G40" s="3" t="n"/>
     </row>
@@ -2883,19 +3373,19 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
+        <v>212000000</v>
+      </c>
+      <c r="C41" s="3" t="n">
         <v>194600000</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="D41" s="3" t="n">
         <v>99000000</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="E41" s="3" t="n">
         <v>75100000</v>
       </c>
-      <c r="E41" s="3" t="n">
-        <v>49200000</v>
-      </c>
       <c r="F41" s="3" t="n">
-        <v>33400000</v>
+        <v>49100000</v>
       </c>
       <c r="G41" s="3" t="n"/>
     </row>
@@ -2906,19 +3396,19 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
+        <v>67400000</v>
+      </c>
+      <c r="C42" s="3" t="n">
         <v>53100000</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="D42" s="3" t="n">
         <v>44900000</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="E42" s="3" t="n">
         <v>39300000</v>
       </c>
-      <c r="E42" s="3" t="n">
-        <v>40000000</v>
-      </c>
       <c r="F42" s="3" t="n">
-        <v>35700000</v>
+        <v>36500000</v>
       </c>
       <c r="G42" s="3" t="n"/>
     </row>
@@ -2929,19 +3419,19 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
+        <v>143800000</v>
+      </c>
+      <c r="C43" s="3" t="n">
         <v>161500000</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="D43" s="3" t="n">
         <v>89500000</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="E43" s="3" t="n">
         <v>63000000</v>
       </c>
-      <c r="E43" s="3" t="n">
-        <v>66100000</v>
-      </c>
       <c r="F43" s="3" t="n">
-        <v>90600000</v>
+        <v>60900000</v>
       </c>
       <c r="G43" s="3" t="n"/>
     </row>
@@ -2952,19 +3442,19 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
+        <v>295200000</v>
+      </c>
+      <c r="C44" s="3" t="n">
         <v>159200000</v>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="D44" s="3" t="n">
         <v>103200000</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="E44" s="3" t="n">
         <v>75400000</v>
       </c>
-      <c r="E44" s="3" t="n">
-        <v>25800000</v>
-      </c>
       <c r="F44" s="3" t="n">
-        <v>10400000</v>
+        <v>26200000</v>
       </c>
       <c r="G44" s="3" t="n"/>
     </row>
@@ -2975,19 +3465,19 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
+        <v>103800000</v>
+      </c>
+      <c r="C45" s="3" t="n">
         <v>68500000</v>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="D45" s="3" t="n">
         <v>42900000</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="E45" s="3" t="n">
         <v>25300000</v>
       </c>
-      <c r="E45" s="3" t="n">
-        <v>29500000</v>
-      </c>
       <c r="F45" s="3" t="n">
-        <v>27500000</v>
+        <v>24700000</v>
       </c>
       <c r="G45" s="3" t="n"/>
     </row>
@@ -2998,19 +3488,19 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
+        <v>399000000</v>
+      </c>
+      <c r="C46" s="3" t="n">
         <v>227700000</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="D46" s="3" t="n">
         <v>146100000</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="E46" s="3" t="n">
         <v>100700000</v>
       </c>
-      <c r="E46" s="3" t="n">
-        <v>55300000</v>
-      </c>
       <c r="F46" s="3" t="n">
-        <v>37900000</v>
+        <v>50900000</v>
       </c>
       <c r="G46" s="3" t="n"/>
     </row>
@@ -3021,19 +3511,19 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
+        <v>399000000</v>
+      </c>
+      <c r="C47" s="3" t="n">
         <v>227700000</v>
       </c>
-      <c r="C47" s="3" t="n">
+      <c r="D47" s="3" t="n">
         <v>146100000</v>
       </c>
-      <c r="D47" s="3" t="n">
+      <c r="E47" s="3" t="n">
         <v>100700000</v>
       </c>
-      <c r="E47" s="3" t="n">
-        <v>55300000</v>
-      </c>
       <c r="F47" s="3" t="n">
-        <v>37900000</v>
+        <v>50900000</v>
       </c>
       <c r="G47" s="3" t="n"/>
     </row>
@@ -3042,7 +3532,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3196,10 +3686,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>4544000000</v>
+        <v>4574300000</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>3240200000</v>
+        <v>3248800000</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>3289500000</v>
@@ -3256,10 +3746,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>4544000000</v>
+        <v>4574300000</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>3240200000</v>
+        <v>3248800000</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>3289500000</v>
@@ -4100,10 +4590,10 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>6700000</v>
+        <v>37000000</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>-7300000</v>
+        <v>1300000</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>5038000000</v>
@@ -4352,10 +4842,10 @@
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>50000000</v>
+        <v>19700000</v>
       </c>
       <c r="C66" s="3" t="n">
-        <v>13500000</v>
+        <v>4900000</v>
       </c>
       <c r="D66" s="3" t="n">
         <v>4200000</v>
@@ -4372,10 +4862,10 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>50000000</v>
+        <v>19700000</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>13500000</v>
+        <v>4900000</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>4200000</v>
@@ -4974,7 +5464,2081 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H90"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Treasury Shares Number</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>68142750</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>69023973</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>110233722</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>123335852</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>126287344</v>
+      </c>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ordinary Shares Number</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>253898194</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>253016971</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>251807222</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>238705092</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>238108831</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Share Issued</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>322040944</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>322040944</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>362040944</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>362040944</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>364396175</v>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Net Debt</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="n">
+        <v>449600000</v>
+      </c>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Total Debt</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>9496200000</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>4973100000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>4569000000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>1224300000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>187800000</v>
+      </c>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Tangible Book Value</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>7029300000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>4574300000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>4792800000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>3759900000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>3143900000</v>
+      </c>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Invested Capital</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>15691300000</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>8721700000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>8917600000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>4761700000</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>3167500000</v>
+      </c>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>9889300000</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>3183600000</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>4422400000</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>1891500000</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>1589800000</v>
+      </c>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Net Tangible Assets</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>7029300000</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>4574300000</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>4792800000</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>3759900000</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>3143900000</v>
+      </c>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capital Lease Obligations</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>1045800000</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>845400000</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>462200000</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>238100000</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>181600000</v>
+      </c>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Common Stock Equity</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>7240900000</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>4594000000</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>4810800000</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>3775500000</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>3161300000</v>
+      </c>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Total Capitalization</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>15672900000</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>8697200000</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>8901600000</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>4753700000</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>3161300000</v>
+      </c>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Total Equity Gross Minority Interest</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>7241900000</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>4594000000</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>4810800000</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>3775500000</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>3161300000</v>
+      </c>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Minority Interest</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Stockholders Equity</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>7240900000</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>4594000000</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>4810800000</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>3775500000</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>3161300000</v>
+      </c>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Gains Losses Not Affecting Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>-13500000</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>-1300000</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>-1900000</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>-16900000</v>
+      </c>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Other Equity Adjustments</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>-13500000</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>-1300000</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>-1900000</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>-16900000</v>
+      </c>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Treasury Stock</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>1061900000</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>1075700000</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>1717900000</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>1922100000</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>1931400000</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>3921700000</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>3300500000</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>3569300000</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>3688900000</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>3104400000</v>
+      </c>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Additional Paid In Capital</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>4386200000</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>2360900000</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>2951800000</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>2001400000</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>1996000000</v>
+      </c>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Capital Stock</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>8400000</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>8400000</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>8900000</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>9200000</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>9200000</v>
+      </c>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>8400000</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>8400000</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>8900000</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>9200000</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>9200000</v>
+      </c>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Preferred Stock</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n"/>
+      <c r="C24" s="3" t="n"/>
+      <c r="D24" s="3" t="n"/>
+      <c r="E24" s="3" t="n"/>
+      <c r="F24" s="3" t="n"/>
+      <c r="G24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Total Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>15061400000</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>7836600000</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>5291400000</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>1321100000</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>275200000</v>
+      </c>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Total Non Current Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>13712400000</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>6308800000</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>4496800000</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>1183000000</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>181700000</v>
+      </c>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Liabilities Heldfor Sale Non Current</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="3" t="n"/>
+      <c r="D27" s="3" t="n"/>
+      <c r="E27" s="3" t="n"/>
+      <c r="F27" s="3" t="n"/>
+      <c r="G27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Non Current Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>142100000</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>143100000</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>600000</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>300000</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>4092500000</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>1302000000</v>
+      </c>
+      <c r="D29" s="3" t="n"/>
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="3" t="n"/>
+      <c r="G29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>4092500000</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>1302000000</v>
+      </c>
+      <c r="D30" s="3" t="n"/>
+      <c r="E30" s="3" t="n"/>
+      <c r="F30" s="3" t="n"/>
+      <c r="G30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Long Term Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>9477800000</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>4863700000</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>4496200000</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>1182700000</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>181600000</v>
+      </c>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Long Term Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>1045800000</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>760500000</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>405400000</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>204500000</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>181600000</v>
+      </c>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Long Term Debt</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>8432000000</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>4103200000</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>4090800000</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>978200000</v>
+      </c>
+      <c r="F33" s="3" t="n"/>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>1349000000</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>1527800000</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>794600000</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>138100000</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>93500000</v>
+      </c>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Other Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n"/>
+      <c r="C35" s="3" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="D35" s="3" t="n"/>
+      <c r="E35" s="3" t="n"/>
+      <c r="F35" s="3" t="n"/>
+      <c r="G35" s="3" t="n">
+        <v>8100000</v>
+      </c>
+      <c r="H35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>685600000</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>293000000</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>15600000</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>19300000</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>19000000</v>
+      </c>
+      <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>685600000</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>293000000</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>15600000</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>19300000</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>19000000</v>
+      </c>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Current Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>18400000</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>109400000</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>72800000</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>41600000</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>6200000</v>
+      </c>
+      <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Current Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n"/>
+      <c r="C39" s="3" t="n">
+        <v>84900000</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>56800000</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>33600000</v>
+      </c>
+      <c r="F39" s="3" t="n"/>
+      <c r="G39" s="3" t="n">
+        <v>13100000</v>
+      </c>
+      <c r="H39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Current Debt</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>18400000</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>24500000</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>6200000</v>
+      </c>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Other Current Borrowings</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n"/>
+      <c r="C41" s="3" t="n">
+        <v>24500000</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="F41" s="3" t="n"/>
+      <c r="G41" s="3" t="n">
+        <v>6100000</v>
+      </c>
+      <c r="H41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Pensionand Other Post Retirement Benefit Plans Current</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n"/>
+      <c r="C42" s="3" t="n">
+        <v>7600000</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>6200000</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="F42" s="3" t="n"/>
+      <c r="G42" s="3" t="n">
+        <v>4800000</v>
+      </c>
+      <c r="H42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Payables And Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>645000000</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>1114600000</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>700000000</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>70700000</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>68300000</v>
+      </c>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Current Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n"/>
+      <c r="C44" s="3" t="n">
+        <v>14200000</v>
+      </c>
+      <c r="D44" s="3" t="n"/>
+      <c r="E44" s="3" t="n"/>
+      <c r="F44" s="3" t="n"/>
+      <c r="G44" s="3" t="n">
+        <v>10900000</v>
+      </c>
+      <c r="H44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>645000000</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>1100400000</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>700000000</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>70700000</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>68300000</v>
+      </c>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Other Payable</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n"/>
+      <c r="C46" s="3" t="n"/>
+      <c r="D46" s="3" t="n">
+        <v>12100000</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>10600000</v>
+      </c>
+      <c r="F46" s="3" t="n"/>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Total Tax Payable</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>23300000</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>18100000</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>36600000</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>7200000</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>6900000</v>
+      </c>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Income Tax Payable</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n"/>
+      <c r="C48" s="3" t="n">
+        <v>17700000</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>36600000</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>6900000</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>5500000</v>
+      </c>
+      <c r="H48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>621700000</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>1082300000</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>651300000</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>52900000</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>61400000</v>
+      </c>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>22303300000</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>12430600000</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>10102200000</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>5096600000</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>3436500000</v>
+      </c>
+      <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Total Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>11065000000</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>7719200000</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>4885200000</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>3067000000</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>1753200000</v>
+      </c>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Other Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>816600000</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>37000000</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>300000</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>45400000</v>
+      </c>
+      <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Non Current Prepaid Assets</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n"/>
+      <c r="C53" s="3" t="n">
+        <v>329400000</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>164000000</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>104400000</v>
+      </c>
+      <c r="F53" s="3" t="n"/>
+      <c r="G53" s="3" t="n">
+        <v>9000000</v>
+      </c>
+      <c r="H53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Assets</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>18600000</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>11800000</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>9000000</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>8800000</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>8900000</v>
+      </c>
+      <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Assets</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>18600000</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>11800000</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>9000000</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>8800000</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>8900000</v>
+      </c>
+      <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Non Current Note Receivables</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n"/>
+      <c r="C56" s="3" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="D56" s="3" t="n"/>
+      <c r="E56" s="3" t="n"/>
+      <c r="F56" s="3" t="n"/>
+      <c r="G56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="3" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Non Current Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n"/>
+      <c r="C57" s="3" t="n"/>
+      <c r="D57" s="3" t="n"/>
+      <c r="E57" s="3" t="n">
+        <v>3800000</v>
+      </c>
+      <c r="F57" s="3" t="n"/>
+      <c r="G57" s="3" t="n">
+        <v>3800000</v>
+      </c>
+      <c r="H57" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Investments And Advances</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>1620500000</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>847700000</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>856800000</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>867400000</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>97100000</v>
+      </c>
+      <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Investmentin Financial Assets</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>1614100000</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>836600000</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>835100000</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>835100000</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>90700000</v>
+      </c>
+      <c r="G59" s="3" t="n"/>
+      <c r="H59" s="3" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Held To Maturity Securities</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n"/>
+      <c r="C60" s="3" t="n"/>
+      <c r="D60" s="3" t="n"/>
+      <c r="E60" s="3" t="n"/>
+      <c r="F60" s="3" t="n"/>
+      <c r="G60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="3" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Available For Sale Securities</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>1614100000</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>836600000</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>835100000</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>835100000</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>90700000</v>
+      </c>
+      <c r="G61" s="3" t="n"/>
+      <c r="H61" s="3" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Long Term Equity Investment</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>6400000</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>11100000</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>21700000</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>32300000</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>6400000</v>
+      </c>
+      <c r="G62" s="3" t="n"/>
+      <c r="H62" s="3" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Goodwill And Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>211600000</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>19700000</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>15600000</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>17400000</v>
+      </c>
+      <c r="G63" s="3" t="n"/>
+      <c r="H63" s="3" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>48300000</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>19700000</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>15600000</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>17400000</v>
+      </c>
+      <c r="G64" s="3" t="n"/>
+      <c r="H64" s="3" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>163300000</v>
+      </c>
+      <c r="C65" s="3" t="n"/>
+      <c r="D65" s="3" t="n"/>
+      <c r="E65" s="3" t="n"/>
+      <c r="F65" s="3" t="n"/>
+      <c r="G65" s="3" t="n"/>
+      <c r="H65" s="3" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Net PPE</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>8397700000</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>6472100000</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>3815400000</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>2066700000</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>1584400000</v>
+      </c>
+      <c r="G66" s="3" t="n"/>
+      <c r="H66" s="3" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n"/>
+      <c r="C67" s="3" t="n">
+        <v>-637000000</v>
+      </c>
+      <c r="D67" s="3" t="n"/>
+      <c r="E67" s="3" t="n">
+        <v>-362800000</v>
+      </c>
+      <c r="F67" s="3" t="n"/>
+      <c r="G67" s="3" t="n">
+        <v>-236300000</v>
+      </c>
+      <c r="H67" s="3" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Gross PPE</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>8397700000</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>7109100000</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>3815400000</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>2429500000</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>1584400000</v>
+      </c>
+      <c r="G68" s="3" t="n"/>
+      <c r="H68" s="3" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Other Properties</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v>8397700000</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>6727700000</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>3815400000</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>2376300000</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>1584400000</v>
+      </c>
+      <c r="G69" s="3" t="n"/>
+      <c r="H69" s="3" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Land And Improvements</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n"/>
+      <c r="C70" s="3" t="n">
+        <v>381400000</v>
+      </c>
+      <c r="D70" s="3" t="n"/>
+      <c r="E70" s="3" t="n">
+        <v>53200000</v>
+      </c>
+      <c r="F70" s="3" t="n"/>
+      <c r="G70" s="3" t="n">
+        <v>48500000</v>
+      </c>
+      <c r="H70" s="3" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n"/>
+      <c r="C71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="3" t="n"/>
+      <c r="E71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="3" t="n"/>
+      <c r="G71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="3" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v>11238300000</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>4711400000</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>5217000000</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>2029600000</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>1683300000</v>
+      </c>
+      <c r="G72" s="3" t="n"/>
+      <c r="H72" s="3" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v>360500000</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>12400000</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>61400000</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>24600000</v>
+      </c>
+      <c r="G73" s="3" t="n"/>
+      <c r="H73" s="3" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Assets Held For Sale Current</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n"/>
+      <c r="C74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="3" t="n"/>
+      <c r="G74" s="3" t="n">
+        <v>21400000</v>
+      </c>
+      <c r="H74" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Current Deferred Assets</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="n"/>
+      <c r="C75" s="3" t="n">
+        <v>8400000</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>5400000</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="F75" s="3" t="n"/>
+      <c r="G75" s="3" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="H75" s="3" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Restricted Cash</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="n"/>
+      <c r="C76" s="3" t="n">
+        <v>6800000</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>107100000</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>74500000</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>80600000</v>
+      </c>
+      <c r="G76" s="3" t="n">
+        <v>600000</v>
+      </c>
+      <c r="H76" s="3" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Prepaid Assets</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="n">
+        <v>53500000</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>152000000</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>72600000</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>52400000</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>22400000</v>
+      </c>
+      <c r="G77" s="3" t="n"/>
+      <c r="H77" s="3" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="n">
+        <v>1526100000</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>853700000</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>237100000</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>215400000</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>108700000</v>
+      </c>
+      <c r="G78" s="3" t="n"/>
+      <c r="H78" s="3" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Other Receivables</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="n"/>
+      <c r="C79" s="3" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>11300000</v>
+      </c>
+      <c r="E79" s="3" t="n"/>
+      <c r="F79" s="3" t="n"/>
+      <c r="G79" s="3" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="H79" s="3" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Taxes Receivable</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="n">
+        <v>46900000</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>131400000</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>133400000</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>158300000</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>84400000</v>
+      </c>
+      <c r="G80" s="3" t="n"/>
+      <c r="H80" s="3" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Accrued Interest Receivable</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="n"/>
+      <c r="C81" s="3" t="n">
+        <v>400000</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="F81" s="3" t="n"/>
+      <c r="G81" s="3" t="n">
+        <v>21600000</v>
+      </c>
+      <c r="H81" s="3" t="n">
+        <v>27500000</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Loans Receivable</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="n"/>
+      <c r="C82" s="3" t="n"/>
+      <c r="D82" s="3" t="n"/>
+      <c r="E82" s="3" t="n"/>
+      <c r="F82" s="3" t="n"/>
+      <c r="G82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" s="3" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="n">
+        <v>1479200000</v>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>720300000</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>91200000</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>54700000</v>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>24300000</v>
+      </c>
+      <c r="G83" s="3" t="n"/>
+      <c r="H83" s="3" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Allowance For Doubtful Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="n"/>
+      <c r="C84" s="3" t="n">
+        <v>-4000000</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>-1500000</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>-700000</v>
+      </c>
+      <c r="F84" s="3" t="n"/>
+      <c r="G84" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="H84" s="3" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Gross Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="n"/>
+      <c r="C85" s="3" t="n">
+        <v>724300000</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>92700000</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>55400000</v>
+      </c>
+      <c r="F85" s="3" t="n"/>
+      <c r="G85" s="3" t="n">
+        <v>11300000</v>
+      </c>
+      <c r="H85" s="3" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Cash Cash Equivalents And Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="n">
+        <v>9298200000</v>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>3678100000</v>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>4794800000</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>1679300000</v>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>1447000000</v>
+      </c>
+      <c r="G86" s="3" t="n"/>
+      <c r="H86" s="3" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Other Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="n"/>
+      <c r="C87" s="3" t="n"/>
+      <c r="D87" s="3" t="n"/>
+      <c r="E87" s="3" t="n"/>
+      <c r="F87" s="3" t="n"/>
+      <c r="G87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Cash And Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="n">
+        <v>9298200000</v>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>3678100000</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>4794800000</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>1679300000</v>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>1447000000</v>
+      </c>
+      <c r="G88" s="3" t="n"/>
+      <c r="H88" s="3" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="n"/>
+      <c r="C89" s="3" t="n">
+        <v>2525400000</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>4229800000</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>1524800000</v>
+      </c>
+      <c r="F89" s="3" t="n"/>
+      <c r="G89" s="3" t="n">
+        <v>1801500000</v>
+      </c>
+      <c r="H89" s="3" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Cash Financial</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="n"/>
+      <c r="C90" s="3" t="n">
+        <v>1152700000</v>
+      </c>
+      <c r="D90" s="3" t="n">
+        <v>565000000</v>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>154500000</v>
+      </c>
+      <c r="F90" s="3" t="n"/>
+      <c r="G90" s="3" t="n">
+        <v>633200000</v>
+      </c>
+      <c r="H90" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6444,13 +9008,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6458,6 +9022,9 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6468,20 +9035,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2024-12-31</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-09-30</t>
         </is>
@@ -6494,17 +9076,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>-214900000</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>-1221700000</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>-1035900000</v>
       </c>
-      <c r="D2" s="3" t="n">
-        <v>-492300000</v>
-      </c>
       <c r="E2" s="3" t="n">
-        <v>-227900000</v>
-      </c>
+        <v>-682200000</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>-741400000</v>
+      </c>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6512,16 +9099,19 @@
           <t>Repayment Of Debt</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="B3" s="3" t="n"/>
       <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="n">
         <v>-800000</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n">
         <v>-100000</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="H3" s="3" t="n">
         <v>-200000</v>
       </c>
     </row>
@@ -6532,15 +9122,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0</v>
+        <v>4337500000</v>
       </c>
       <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="n">
         <v>3162500000</v>
       </c>
-      <c r="D4" s="3" t="n"/>
       <c r="E4" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>1000000000</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6548,16 +9145,19 @@
           <t>Issuance Of Capital Stock</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="B5" s="3" t="n"/>
       <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
         <v>1150000000</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n">
         <v>700000000</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="H5" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6568,17 +9168,22 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>-2472900000</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>-2056000000</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>-955500000</v>
       </c>
-      <c r="D6" s="3" t="n">
-        <v>-417700000</v>
-      </c>
       <c r="E6" s="3" t="n">
-        <v>-172100000</v>
-      </c>
+        <v>-510600000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>-543900000</v>
+      </c>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6587,17 +9192,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>9626900000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>3721600000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>4923600000</v>
       </c>
-      <c r="D7" s="3" t="n">
-        <v>2450300000</v>
-      </c>
       <c r="E7" s="3" t="n">
-        <v>2278700000</v>
-      </c>
+        <v>1753800000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>1520300000</v>
+      </c>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6611,10 +9221,17 @@
       <c r="C8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="3" t="n"/>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="E8" s="3" t="n">
-        <v>-10400000</v>
-      </c>
+        <v>7300000</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>-7300000</v>
+      </c>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6623,17 +9240,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>3721600000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>4923600000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>1753800000</v>
       </c>
-      <c r="D9" s="3" t="n">
-        <v>2278700000</v>
-      </c>
       <c r="E9" s="3" t="n">
-        <v>2326300000</v>
-      </c>
+        <v>1520300000</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>2450300000</v>
+      </c>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6642,17 +9264,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>-5100000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>-11700000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>1600000</v>
       </c>
-      <c r="D10" s="3" t="n">
-        <v>-6700000</v>
-      </c>
       <c r="E10" s="3" t="n">
-        <v>7300000</v>
-      </c>
+        <v>100000</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>300000</v>
+      </c>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6661,17 +9288,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>5910400000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>-1190300000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>3168200000</v>
       </c>
-      <c r="D11" s="3" t="n">
-        <v>167900000</v>
-      </c>
       <c r="E11" s="3" t="n">
-        <v>-44500000</v>
-      </c>
+        <v>226100000</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>-923000000</v>
+      </c>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6680,17 +9312,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>6295500000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>106400000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>4200600000</v>
       </c>
-      <c r="D12" s="3" t="n">
-        <v>658500000</v>
-      </c>
       <c r="E12" s="3" t="n">
-        <v>-1300000</v>
-      </c>
+        <v>1000000000</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>-181500000</v>
+      </c>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6710,6 +9347,11 @@
       <c r="E13" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="F13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6718,17 +9360,22 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>6295500000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>106400000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>4200600000</v>
       </c>
-      <c r="D14" s="3" t="n">
-        <v>658500000</v>
-      </c>
       <c r="E14" s="3" t="n">
-        <v>-1300000</v>
-      </c>
+        <v>1000000000</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>-181500000</v>
+      </c>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6737,13 +9384,22 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>-43800000</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>100000000</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>-113100000</v>
       </c>
-      <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3" t="n"/>
+      <c r="E15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>-181500000</v>
+      </c>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6752,17 +9408,22 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>2001800000</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>6400000</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>2000000</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3" t="n">
         <v>-8900000</v>
       </c>
-      <c r="E16" s="3" t="n">
-        <v>-1100000</v>
-      </c>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6770,16 +9431,19 @@
           <t>Net Common Stock Issuance</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3" t="n">
         <v>1150000000</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3" t="n"/>
+      <c r="G17" s="3" t="n">
         <v>700000000</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="H17" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6789,16 +9453,19 @@
           <t>Common Stock Issuance</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="B18" s="3" t="n"/>
       <c r="C18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3" t="n">
         <v>1150000000</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="n"/>
+      <c r="G18" s="3" t="n">
         <v>700000000</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="H18" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6809,17 +9476,22 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>0</v>
+        <v>4337500000</v>
       </c>
       <c r="C19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="3" t="n">
         <v>3161700000</v>
       </c>
-      <c r="D19" s="3" t="n">
-        <v>-100000</v>
-      </c>
       <c r="E19" s="3" t="n">
-        <v>-200000</v>
-      </c>
+        <v>1000000000</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -6828,17 +9500,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0</v>
+        <v>4337500000</v>
       </c>
       <c r="C20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="3" t="n">
         <v>3161700000</v>
       </c>
-      <c r="D20" s="3" t="n">
-        <v>-100000</v>
-      </c>
       <c r="E20" s="3" t="n">
-        <v>-200000</v>
-      </c>
+        <v>1000000000</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6846,16 +9523,19 @@
           <t>Long Term Debt Payments</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="B21" s="3" t="n"/>
       <c r="C21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="n">
         <v>-800000</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n"/>
+      <c r="F21" s="3" t="n"/>
+      <c r="G21" s="3" t="n">
         <v>-100000</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="H21" s="3" t="n">
         <v>-200000</v>
       </c>
     </row>
@@ -6866,15 +9546,22 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>0</v>
+        <v>4337500000</v>
       </c>
       <c r="C22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="n">
         <v>3162500000</v>
       </c>
-      <c r="D22" s="3" t="n"/>
       <c r="E22" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>1000000000</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -6883,17 +9570,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>-2643100000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>-2131000000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>-952000000</v>
       </c>
-      <c r="D23" s="3" t="n">
-        <v>-416000000</v>
-      </c>
       <c r="E23" s="3" t="n">
-        <v>12600000</v>
-      </c>
+        <v>-602300000</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>-544000000</v>
+      </c>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6902,17 +9594,22 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>-42700000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>42700000</v>
       </c>
-      <c r="D24" s="3" t="n">
-        <v>100000</v>
-      </c>
       <c r="E24" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>-42700000</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6921,17 +9618,22 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
+        <v>-2643100000</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>-2088300000</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>-994700000</v>
       </c>
-      <c r="D25" s="3" t="n">
-        <v>-416100000</v>
-      </c>
       <c r="E25" s="3" t="n">
-        <v>12600000</v>
-      </c>
+        <v>-559600000</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>-543900000</v>
+      </c>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -6939,16 +9641,19 @@
           <t>Net Other Investing Changes</t>
         </is>
       </c>
-      <c r="B26" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="B26" s="3" t="n"/>
       <c r="C26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="3" t="n">
         <v>3500000</v>
       </c>
-      <c r="D26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3" t="n">
+      <c r="E26" s="3" t="n"/>
+      <c r="F26" s="3" t="n"/>
+      <c r="G26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3" t="n">
         <v>500000</v>
       </c>
     </row>
@@ -6958,16 +9663,19 @@
           <t>Net Investment Purchase And Sale</t>
         </is>
       </c>
-      <c r="B27" s="3" t="n">
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="3" t="n">
         <v>-75000000</v>
       </c>
-      <c r="C27" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="D27" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="E27" s="3" t="n"/>
+      <c r="F27" s="3" t="n"/>
+      <c r="G27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6977,16 +9685,19 @@
           <t>Sale Of Investment</t>
         </is>
       </c>
-      <c r="B28" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="B28" s="3" t="n"/>
       <c r="C28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="E28" s="3" t="n"/>
+      <c r="F28" s="3" t="n"/>
+      <c r="G28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6996,16 +9707,19 @@
           <t>Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B29" s="3" t="n">
+      <c r="B29" s="3" t="n"/>
+      <c r="C29" s="3" t="n">
         <v>-75000000</v>
       </c>
-      <c r="C29" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="D29" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="3" t="n"/>
+      <c r="G29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7016,17 +9730,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
+        <v>-170200000</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>42700000</v>
       </c>
-      <c r="C30" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="D30" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E30" s="3" t="n">
-        <v>184200000</v>
-      </c>
+      <c r="E30" s="3" t="n"/>
+      <c r="F30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -7034,16 +9753,19 @@
           <t>Sale Of Business</t>
         </is>
       </c>
-      <c r="B31" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="B31" s="3" t="n"/>
       <c r="C31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="E31" s="3" t="n"/>
+      <c r="F31" s="3" t="n"/>
+      <c r="G31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="3" t="n">
         <v>184200000</v>
       </c>
     </row>
@@ -7053,12 +9775,19 @@
           <t>Purchase Of Business</t>
         </is>
       </c>
-      <c r="B32" s="3" t="n"/>
-      <c r="C32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="3" t="n"/>
-      <c r="E32" s="3" t="n">
+      <c r="B32" s="3" t="n">
+        <v>-170200000</v>
+      </c>
+      <c r="C32" s="3" t="n"/>
+      <c r="D32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3" t="n"/>
+      <c r="F32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7069,17 +9798,22 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
+        <v>-2472900000</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>-2056000000</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="D33" s="3" t="n">
         <v>-955500000</v>
       </c>
-      <c r="D33" s="3" t="n">
-        <v>-416100000</v>
-      </c>
       <c r="E33" s="3" t="n">
-        <v>-172100000</v>
-      </c>
+        <v>-510600000</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>-543900000</v>
+      </c>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -7088,17 +9822,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>-2472900000</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>-2056000000</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="D34" s="3" t="n">
         <v>-955500000</v>
       </c>
-      <c r="D34" s="3" t="n">
-        <v>-417700000</v>
-      </c>
       <c r="E34" s="3" t="n">
-        <v>-172100000</v>
-      </c>
+        <v>-510600000</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>-543900000</v>
+      </c>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -7107,17 +9846,22 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
+        <v>2258000000</v>
+      </c>
+      <c r="C35" s="3" t="n">
         <v>834300000</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="D35" s="3" t="n">
         <v>-80400000</v>
       </c>
-      <c r="D35" s="3" t="n">
-        <v>-74600000</v>
-      </c>
       <c r="E35" s="3" t="n">
-        <v>-55800000</v>
-      </c>
+        <v>-171600000</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>-197500000</v>
+      </c>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -7132,11 +9876,16 @@
         <v>0</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>36300000</v>
+        <v>0</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>-21000000</v>
-      </c>
+        <v>-3700000</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>-13400000</v>
+      </c>
+      <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -7145,17 +9894,22 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>2258000000</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>834300000</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>-80400000</v>
       </c>
-      <c r="D37" s="3" t="n">
-        <v>-110900000</v>
-      </c>
       <c r="E37" s="3" t="n">
-        <v>-34800000</v>
-      </c>
+        <v>-167900000</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>-184100000</v>
+      </c>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -7164,17 +9918,22 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
+        <v>2121700000</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>787500000</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>-98500000</v>
       </c>
-      <c r="D38" s="3" t="n">
-        <v>-34900000</v>
-      </c>
       <c r="E38" s="3" t="n">
-        <v>-13200000</v>
-      </c>
+        <v>-168000000</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>-157600000</v>
+      </c>
+      <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -7183,17 +9942,22 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
+        <v>3198000000</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>1566500000</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>-3700000</v>
       </c>
-      <c r="D39" s="3" t="n">
-        <v>-800000</v>
-      </c>
       <c r="E39" s="3" t="n">
-        <v>3700000</v>
-      </c>
+        <v>600000</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -7202,17 +9966,22 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
+        <v>-318900000</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>-166900000</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>-80600000</v>
       </c>
-      <c r="D40" s="3" t="n">
-        <v>26400000</v>
-      </c>
       <c r="E40" s="3" t="n">
-        <v>-19000000</v>
-      </c>
+        <v>-72600000</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>-19100000</v>
+      </c>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -7221,17 +9990,22 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
+        <v>-64900000</v>
+      </c>
+      <c r="C41" s="3" t="n">
         <v>25400000</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="D41" s="3" t="n">
         <v>-4300000</v>
       </c>
-      <c r="D41" s="3" t="n">
-        <v>-20200000</v>
-      </c>
       <c r="E41" s="3" t="n">
-        <v>3400000</v>
-      </c>
+        <v>6900000</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>-57000000</v>
+      </c>
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -7240,17 +10014,22 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
+        <v>-64900000</v>
+      </c>
+      <c r="C42" s="3" t="n">
         <v>25400000</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="D42" s="3" t="n">
         <v>-4300000</v>
       </c>
-      <c r="D42" s="3" t="n">
-        <v>-20200000</v>
-      </c>
       <c r="E42" s="3" t="n">
-        <v>3400000</v>
-      </c>
+        <v>6900000</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>-57000000</v>
+      </c>
+      <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -7259,17 +10038,22 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
+        <v>-64900000</v>
+      </c>
+      <c r="C43" s="3" t="n">
         <v>25400000</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="D43" s="3" t="n">
         <v>-4300000</v>
       </c>
-      <c r="D43" s="3" t="n">
-        <v>-20200000</v>
-      </c>
       <c r="E43" s="3" t="n">
-        <v>3400000</v>
-      </c>
+        <v>6900000</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>-57000000</v>
+      </c>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -7278,17 +10062,22 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
+        <v>-19000000</v>
+      </c>
+      <c r="C44" s="3" t="n">
         <v>-11900000</v>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="D44" s="3" t="n">
         <v>-700000</v>
       </c>
-      <c r="D44" s="3" t="n">
-        <v>-8200000</v>
-      </c>
       <c r="E44" s="3" t="n">
-        <v>4500000</v>
-      </c>
+        <v>-6500000</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -7297,17 +10086,22 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
+        <v>-673500000</v>
+      </c>
+      <c r="C45" s="3" t="n">
         <v>-625600000</v>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="D45" s="3" t="n">
         <v>-9200000</v>
       </c>
-      <c r="D45" s="3" t="n">
-        <v>-32100000</v>
-      </c>
       <c r="E45" s="3" t="n">
-        <v>-5800000</v>
-      </c>
+        <v>-96400000</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>-85200000</v>
+      </c>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -7316,17 +10110,22 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
+        <v>-758900000</v>
+      </c>
+      <c r="C46" s="3" t="n">
         <v>-632800000</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="D46" s="3" t="n">
         <v>-37300000</v>
       </c>
-      <c r="D46" s="3" t="n">
-        <v>-1900000</v>
-      </c>
       <c r="E46" s="3" t="n">
-        <v>-6000000</v>
-      </c>
+        <v>-35000000</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>-9500000</v>
+      </c>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -7335,13 +10134,22 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
+        <v>19700000</v>
+      </c>
+      <c r="C47" s="3" t="n">
         <v>67000000</v>
       </c>
-      <c r="C47" s="3" t="n">
+      <c r="D47" s="3" t="n">
         <v>5700000</v>
       </c>
-      <c r="D47" s="3" t="n"/>
-      <c r="E47" s="3" t="n"/>
+      <c r="E47" s="3" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -7350,17 +10158,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
+        <v>35300000</v>
+      </c>
+      <c r="C48" s="3" t="n">
         <v>24900000</v>
       </c>
-      <c r="C48" s="3" t="n">
+      <c r="D48" s="3" t="n">
         <v>26200000</v>
       </c>
-      <c r="D48" s="3" t="n">
-        <v>42600000</v>
-      </c>
       <c r="E48" s="3" t="n">
-        <v>6900000</v>
-      </c>
+        <v>14600000</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>17500000</v>
+      </c>
+      <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -7369,15 +10182,22 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
+        <v>-780600000</v>
+      </c>
+      <c r="C49" s="3" t="n">
         <v>-1500000</v>
       </c>
-      <c r="C49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" s="3" t="n"/>
+      <c r="D49" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="E49" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>-597400000</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -7386,17 +10206,22 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
+        <v>800000</v>
+      </c>
+      <c r="C50" s="3" t="n">
         <v>3700000</v>
       </c>
-      <c r="C50" s="3" t="n">
+      <c r="D50" s="3" t="n">
         <v>900000</v>
       </c>
-      <c r="D50" s="3" t="n">
-        <v>300000</v>
-      </c>
       <c r="E50" s="3" t="n">
-        <v>-700000</v>
-      </c>
+        <v>700000</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>200000</v>
+      </c>
+      <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -7405,17 +10230,22 @@
         </is>
       </c>
       <c r="B51" s="3" t="n">
+        <v>-7800000</v>
+      </c>
+      <c r="C51" s="3" t="n">
         <v>-2800000</v>
       </c>
-      <c r="C51" s="3" t="n">
+      <c r="D51" s="3" t="n">
         <v>-200000</v>
       </c>
-      <c r="D51" s="3" t="n">
-        <v>-600000</v>
-      </c>
       <c r="E51" s="3" t="n">
-        <v>-3500000</v>
-      </c>
+        <v>400000</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>-800000</v>
+      </c>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -7424,17 +10254,22 @@
         </is>
       </c>
       <c r="B52" s="3" t="n">
+        <v>-7800000</v>
+      </c>
+      <c r="C52" s="3" t="n">
         <v>-2800000</v>
       </c>
-      <c r="C52" s="3" t="n">
+      <c r="D52" s="3" t="n">
         <v>-200000</v>
       </c>
-      <c r="D52" s="3" t="n">
-        <v>-600000</v>
-      </c>
       <c r="E52" s="3" t="n">
-        <v>-3500000</v>
-      </c>
+        <v>400000</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>-800000</v>
+      </c>
+      <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -7443,17 +10278,22 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
+        <v>241800000</v>
+      </c>
+      <c r="C53" s="3" t="n">
         <v>215900000</v>
       </c>
-      <c r="C53" s="3" t="n">
+      <c r="D53" s="3" t="n">
         <v>111800000</v>
       </c>
-      <c r="D53" s="3" t="n">
-        <v>37300000</v>
-      </c>
       <c r="E53" s="3" t="n">
-        <v>25300000</v>
-      </c>
+        <v>84700000</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>56100000</v>
+      </c>
+      <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -7462,17 +10302,22 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
+        <v>241800000</v>
+      </c>
+      <c r="C54" s="3" t="n">
         <v>215900000</v>
       </c>
-      <c r="C54" s="3" t="n">
+      <c r="D54" s="3" t="n">
         <v>111800000</v>
       </c>
-      <c r="D54" s="3" t="n">
-        <v>37300000</v>
-      </c>
       <c r="E54" s="3" t="n">
-        <v>25300000</v>
-      </c>
+        <v>84700000</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>56100000</v>
+      </c>
+      <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -7481,17 +10326,22 @@
         </is>
       </c>
       <c r="B55" s="3" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="C55" s="3" t="n">
         <v>3000000</v>
       </c>
-      <c r="C55" s="3" t="n">
+      <c r="D55" s="3" t="n">
         <v>800000</v>
       </c>
-      <c r="D55" s="3" t="n">
-        <v>700000</v>
-      </c>
       <c r="E55" s="3" t="n">
+        <v>2600000</v>
+      </c>
+      <c r="F55" s="3" t="n">
         <v>500000</v>
       </c>
+      <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -7500,17 +10350,22 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="C56" s="3" t="n">
         <v>3000000</v>
       </c>
-      <c r="C56" s="3" t="n">
+      <c r="D56" s="3" t="n">
         <v>800000</v>
       </c>
-      <c r="D56" s="3" t="n">
-        <v>700000</v>
-      </c>
       <c r="E56" s="3" t="n">
+        <v>2600000</v>
+      </c>
+      <c r="F56" s="3" t="n">
         <v>500000</v>
       </c>
+      <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -7519,17 +10374,22 @@
         </is>
       </c>
       <c r="B57" s="3" t="n">
+        <v>238600000</v>
+      </c>
+      <c r="C57" s="3" t="n">
         <v>212900000</v>
       </c>
-      <c r="C57" s="3" t="n">
+      <c r="D57" s="3" t="n">
         <v>111000000</v>
       </c>
-      <c r="D57" s="3" t="n">
-        <v>36600000</v>
-      </c>
       <c r="E57" s="3" t="n">
-        <v>24800000</v>
-      </c>
+        <v>82100000</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>55600000</v>
+      </c>
+      <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -7538,17 +10398,22 @@
         </is>
       </c>
       <c r="B58" s="3" t="n">
+        <v>5900000</v>
+      </c>
+      <c r="C58" s="3" t="n">
         <v>8400000</v>
       </c>
-      <c r="C58" s="3" t="n">
+      <c r="D58" s="3" t="n">
         <v>-6700000</v>
       </c>
-      <c r="D58" s="3" t="n">
-        <v>9200000</v>
-      </c>
       <c r="E58" s="3" t="n">
-        <v>-6000000</v>
-      </c>
+        <v>-7900000</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>3300000</v>
+      </c>
+      <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="n"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -7557,17 +10422,22 @@
         </is>
       </c>
       <c r="B59" s="3" t="n">
+        <v>7600000</v>
+      </c>
+      <c r="C59" s="3" t="n">
         <v>10600000</v>
       </c>
-      <c r="C59" s="3" t="n">
+      <c r="D59" s="3" t="n">
         <v>7500000</v>
       </c>
-      <c r="D59" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="E59" s="3" t="n">
-        <v>-400000</v>
-      </c>
+        <v>6300000</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="G59" s="3" t="n"/>
+      <c r="H59" s="3" t="n"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -7576,17 +10446,22 @@
         </is>
       </c>
       <c r="B60" s="3" t="n">
+        <v>-1700000</v>
+      </c>
+      <c r="C60" s="3" t="n">
         <v>-2200000</v>
       </c>
-      <c r="C60" s="3" t="n">
+      <c r="D60" s="3" t="n">
         <v>-14200000</v>
       </c>
-      <c r="D60" s="3" t="n">
-        <v>9200000</v>
-      </c>
       <c r="E60" s="3" t="n">
-        <v>-5600000</v>
-      </c>
+        <v>-14200000</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>3400000</v>
+      </c>
+      <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="n"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -7595,24 +10470,29 @@
         </is>
       </c>
       <c r="B61" s="3" t="n">
+        <v>621200000</v>
+      </c>
+      <c r="C61" s="3" t="n">
         <v>-268800000</v>
       </c>
-      <c r="C61" s="3" t="n">
+      <c r="D61" s="3" t="n">
         <v>-119600000</v>
       </c>
-      <c r="D61" s="3" t="n">
-        <v>-164400000</v>
-      </c>
       <c r="E61" s="3" t="n">
-        <v>-43600000</v>
-      </c>
+        <v>502500000</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>-104300000</v>
+      </c>
+      <c r="G61" s="3" t="n"/>
+      <c r="H61" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
